--- a/InputData/dist-heat/BFoHPbF/BAU Frac of Heat Provided by Fuel.xlsx
+++ b/InputData/dist-heat/BFoHPbF/BAU Frac of Heat Provided by Fuel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\dist-heat\BFoHPbF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\dist-heat\BFoHPbF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48BF3CEA-6821-4723-B4C9-B7249333D860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0B4272F-B280-4566-B791-AE08EEB29323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32625" yWindow="2040" windowWidth="24900" windowHeight="14490" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11235" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,9 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -32,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
   <si>
     <t>Source:</t>
   </si>
@@ -140,12 +143,6 @@
   </si>
   <si>
     <t>This can be changed by altering dist-heat/EoCtUH.</t>
-  </si>
-  <si>
-    <t>green hydrogen</t>
-  </si>
-  <si>
-    <t>low carbon hydrogen</t>
   </si>
 </sst>
 </file>
@@ -533,17 +530,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="58.1796875" customWidth="1"/>
+    <col min="2" max="2" width="58.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -551,72 +548,72 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="2">
         <v>2014</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -633,15 +630,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.453125" customWidth="1"/>
-    <col min="2" max="2" width="19.453125" customWidth="1"/>
-    <col min="3" max="3" width="17.453125" customWidth="1"/>
-    <col min="4" max="4" width="12.453125" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>14</v>
       </c>
@@ -653,7 +650,7 @@
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B2">
         <v>2000</v>
       </c>
@@ -676,7 +673,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -702,7 +699,7 @@
         <v>8544</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -728,7 +725,7 @@
         <v>12343.4</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -754,7 +751,7 @@
         <v>199.7</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -780,7 +777,7 @@
         <v>4055.7</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -806,7 +803,7 @@
         <v>2641.4</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
         <v>16</v>
       </c>
@@ -817,7 +814,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -834,7 +831,7 @@
         <v>0.63892242256425869</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -851,7 +848,7 @@
         <v>0.17030120384160674</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -868,7 +865,7 @@
         <v>3.3910556428748871E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -885,7 +882,7 @@
         <v>0.15686581716538556</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -908,14 +905,14 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AK13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AK11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.1796875" customWidth="1"/>
-    <col min="2" max="2" width="9.453125" customWidth="1"/>
+    <col min="1" max="1" width="24.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:37" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>32</v>
       </c>
@@ -1028,7 +1025,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1176,7 +1173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -1185,7 +1182,7 @@
         <v>0.17030120384160674</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:R13" si="1">$B3</f>
+        <f t="shared" ref="C3:R11" si="1">$B3</f>
         <v>0.17030120384160674</v>
       </c>
       <c r="D3">
@@ -1325,7 +1322,7 @@
         <v>0.17030120384160674</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -1474,7 +1471,7 @@
         <v>0.63892242256425869</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1623,7 +1620,7 @@
         <v>0.15686581716538556</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1772,7 +1769,7 @@
         <v>3.3910556428748871E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -1920,7 +1917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -1992,7 +1989,7 @@
         <v>0</v>
       </c>
       <c r="S8">
-        <f t="shared" ref="S8:AH13" si="2">$B8</f>
+        <f t="shared" ref="S8:AH11" si="2">$B8</f>
         <v>0</v>
       </c>
       <c r="T8">
@@ -2056,7 +2053,7 @@
         <v>0</v>
       </c>
       <c r="AI8">
-        <f t="shared" ref="AI8:AK13" si="3">$B8</f>
+        <f t="shared" ref="AI8:AK11" si="3">$B8</f>
         <v>0</v>
       </c>
       <c r="AJ8">
@@ -2068,7 +2065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -2216,7 +2213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -2364,7 +2361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -2508,302 +2505,6 @@
         <v>0</v>
       </c>
       <c r="AK11">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="X12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Y12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Z12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AA12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AD12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AE12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AG12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AI12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AJ12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AK12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="X13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Y13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Z13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AA13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AD13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AE13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AG13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AI13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AJ13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AK13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
